--- a/DEV/org.openl.rules.test/test-resources/functionality/no-dublicated-errors.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/no-dublicated-errors.xlsx
@@ -648,36 +648,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C35" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C36" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C37" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C39" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C40" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C41" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>29</v>
